--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Overnight Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Overnight Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="49">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Overnight Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -103,10 +103,10 @@
     <t>Treasury Bills</t>
   </si>
   <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z471</t>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y357</t>
   </si>
   <si>
     <t>SOV</t>
@@ -115,34 +115,19 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X318</t>
-  </si>
-  <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002023Z505</t>
-  </si>
-  <si>
-    <t>IN002023Z513</t>
-  </si>
-  <si>
-    <t>IN002024X342</t>
-  </si>
-  <si>
-    <t>IN002024X326</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y217</t>
+    <t>IN002024X508</t>
+  </si>
+  <si>
+    <t>IN002024Y340</t>
+  </si>
+  <si>
+    <t>IN002024X482</t>
   </si>
   <si>
     <t>Reverse Repo</t>
   </si>
   <si>
-    <t>Reverse Repo ( 2/3/2025 )</t>
+    <t>Reverse Repo (2-6-2025)</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -166,7 +151,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -176,9 +161,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - CRISIL Liquid Overnight Index</t>
   </si>
 </sst>
 </file>
@@ -549,13 +531,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -573,7 +555,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13030200"/>
+          <a:off x="666750" y="12268200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -588,13 +570,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -612,7 +594,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15887700"/>
+          <a:off x="666750" y="15125700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -946,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J80"/>
+  <dimension ref="B1:J75"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -954,7 +936,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.142857142857142" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.0" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
@@ -1416,10 +1398,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="9">
-        <v>47893.58000000001</v>
+        <v>40430.479999999996</v>
       </c>
       <c r="H25" s="10">
-        <v>0.042814095079299994</v>
+        <v>0.04686375928020001</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>13</v>
@@ -1564,10 +1546,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="9">
-        <v>47893.58000000001</v>
+        <v>40430.479999999996</v>
       </c>
       <c r="H33" s="10">
-        <v>0.042814095079299994</v>
+        <v>0.04686375928020001</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>13</v>
@@ -1590,16 +1572,16 @@
         <v>31</v>
       </c>
       <c r="F34" s="14">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="G34" s="15">
-        <v>9991.29</v>
+        <v>19965.70</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0089316363493</v>
+        <v>0.0231426329507</v>
       </c>
       <c r="I34" s="15">
-        <v>6.37</v>
+        <v>5.70</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -1622,13 +1604,13 @@
         <v>10000000</v>
       </c>
       <c r="G35" s="15">
-        <v>9991.29</v>
+        <v>9971.48</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0089316363493</v>
+        <v>0.0115581372862</v>
       </c>
       <c r="I35" s="15">
-        <v>6.37</v>
+        <v>5.80</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -1648,16 +1630,16 @@
         <v>31</v>
       </c>
       <c r="F36" s="14">
-        <v>10000000</v>
+        <v>5500000</v>
       </c>
       <c r="G36" s="15">
-        <v>9978.93</v>
+        <v>5496.49</v>
       </c>
       <c r="H36" s="16">
-        <v>0.008920587223</v>
+        <v>0.0063710889469</v>
       </c>
       <c r="I36" s="15">
-        <v>6.42</v>
+        <v>5.83</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -1665,7 +1647,7 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>35</v>
@@ -1677,16 +1659,16 @@
         <v>31</v>
       </c>
       <c r="F37" s="14">
-        <v>6500000</v>
+        <v>5000000</v>
       </c>
       <c r="G37" s="15">
-        <v>6478.34</v>
+        <v>4996.81</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0057912618918</v>
+        <v>0.0057919000964</v>
       </c>
       <c r="I37" s="15">
-        <v>6.43</v>
+        <v>5.83</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -1694,57 +1676,36 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G38" s="15">
-        <v>4977.22</v>
-      </c>
-      <c r="H38" s="16">
-        <v>0.0044493472885</v>
-      </c>
-      <c r="I38" s="15">
-        <v>6.43</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="14">
-        <v>3500000</v>
-      </c>
-      <c r="G39" s="15">
-        <v>3484.05</v>
-      </c>
-      <c r="H39" s="16">
-        <v>0.0031145395262</v>
-      </c>
-      <c r="I39" s="15">
-        <v>6.43</v>
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9">
+        <v>763957.6500000001</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0.885518237973</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -1752,166 +1713,145 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="14">
-        <v>2000000</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
       <c r="G40" s="15">
-        <v>1995.79</v>
+        <v>599778.14</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0017841210203</v>
-      </c>
-      <c r="I40" s="15">
-        <v>6.42</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>0.6952145602672127</v>
+      </c>
+      <c r="I40" s="9"/>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" s="14">
-        <v>1000000</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
       <c r="G41" s="15">
-        <v>996.67</v>
+        <v>124199.04</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0008909654309</v>
-      </c>
-      <c r="I41" s="15">
-        <v>6.43</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>0.14396153380850119</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="15">
+        <v>19990.31</v>
+      </c>
+      <c r="H42" s="16">
+        <v>0.02317115888260827</v>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="9">
-        <v>1014251.3699999999</v>
-      </c>
-      <c r="H43" s="10">
-        <v>0.9066821605317</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="B43" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="15">
+        <v>19990.16</v>
+      </c>
+      <c r="H43" s="16">
+        <v>0.023170985014677636</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="11"/>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="15">
-        <v>582145.63</v>
-      </c>
-      <c r="H44" s="16">
-        <v>0.5204045793425822</v>
-      </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="11"/>
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="15">
-        <v>231498.31</v>
-      </c>
-      <c r="H45" s="16">
-        <v>0.20694612211392654</v>
-      </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="15">
-        <v>101932.20</v>
-      </c>
-      <c r="H46" s="16">
-        <v>0.09112150109666538</v>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="11"/>
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="15">
-        <v>98675.23</v>
-      </c>
-      <c r="H47" s="16">
-        <v>0.088209957978526</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9">
+        <v>52931.22</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0.0613536112481</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
@@ -1922,140 +1862,111 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="18">
+        <v>5404.4395727398805</v>
+      </c>
+      <c r="H49" s="19">
+        <v>0.006264391498252766</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="18">
+        <v>862723.78957274</v>
+      </c>
+      <c r="H50" s="19">
+        <v>0.9999999999995528</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="15" customHeight="1">
+      <c r="B53" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+    </row>
+    <row r="54" spans="2:8" ht="15" customHeight="1">
+      <c r="B54" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+    </row>
+    <row r="55" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B55" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9">
-        <v>50002.95</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0.0446997500619</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="17" t="s">
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+    </row>
+    <row r="56" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B56" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="18">
-        <v>6492.583016570192</v>
-      </c>
-      <c r="H53" s="19">
-        <v>0.005803994326275441</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="17" t="s">
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+    </row>
+    <row r="57" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B57" s="22" t="s">
         <v>46</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="18">
-        <v>1118640.48301657</v>
-      </c>
-      <c r="H54" s="19">
-        <v>0.9999999999991754</v>
-      </c>
-      <c r="I54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15" customHeight="1">
-      <c r="B57" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
@@ -2063,77 +1974,27 @@
       <c r="F57" s="21"/>
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-    </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
-      <c r="B58" s="13" t="s">
+    </row>
+    <row r="60" ht="15">
+      <c r="B60" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" ht="15">
+      <c r="B75" s="21" t="s">
         <v>48</v>
-      </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-    </row>
-    <row r="59" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B59" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B60" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-    </row>
-    <row r="61" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B61" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-    </row>
-    <row r="64" ht="15">
-      <c r="B64" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" ht="15">
-      <c r="B79" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" ht="15">
-      <c r="B80" s="21" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B57:H57"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B54:H54"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
